--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513670_FASEFINALBFFB4_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513670_FASEFINALBFFB4_PROCESSED.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.5925</v>
+        <v>7.2996</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3412</v>
+        <v>6.104</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2513</v>
+        <v>1.1956</v>
       </c>
       <c r="G2" t="n">
         <v>2.7682</v>
@@ -610,13 +610,13 @@
         <v>1.3632</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1932</v>
+        <v>0.9003</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5344</v>
+        <v>0.2972</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6588000000000001</v>
+        <v>0.6031</v>
       </c>
       <c r="V2" t="n">
         <v>4.6047</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. VALEIRAS CREUS</t>
+          <t>J. CEBOLLA HERRERA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2061</v>
+        <v>3.2019</v>
       </c>
       <c r="E3" t="n">
-        <v>2.891</v>
+        <v>1.3312</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3151</v>
+        <v>1.8707</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.3763</v>
+        <v>4.0595</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.8268</v>
+        <v>1.0719</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4506</v>
+        <v>2.9876</v>
       </c>
       <c r="J3" t="n">
-        <v>-2.2055</v>
+        <v>2.4766</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.2007</v>
+        <v>0.0205</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.0048</v>
+        <v>2.456</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8292</v>
+        <v>1.583</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6262</v>
+        <v>1.0514</v>
       </c>
       <c r="O3" t="n">
-        <v>1.4554</v>
+        <v>0.5316</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7789</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.5842000000000001</v>
+        <v>-0.9737</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3632</v>
+        <v>0.3895</v>
       </c>
       <c r="S3" t="n">
-        <v>4.0829</v>
+        <v>-0.2734</v>
       </c>
       <c r="T3" t="n">
-        <v>3.2386</v>
+        <v>-0.1717</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8444</v>
+        <v>-0.1018</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.2795</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2.4421</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.7216</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. CEBOLLA HERRERA</t>
+          <t>M. BOTAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1417</v>
+        <v>2.8051</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1319</v>
+        <v>0.7643</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0098</v>
+        <v>2.0408</v>
       </c>
       <c r="G4" t="n">
-        <v>4.0595</v>
+        <v>2.8555</v>
       </c>
       <c r="H4" t="n">
-        <v>1.0719</v>
+        <v>-0.0379</v>
       </c>
       <c r="I4" t="n">
-        <v>2.9876</v>
+        <v>2.8935</v>
       </c>
       <c r="J4" t="n">
-        <v>2.4766</v>
+        <v>1.9185</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0205</v>
+        <v>-0.0512</v>
       </c>
       <c r="L4" t="n">
-        <v>2.456</v>
+        <v>1.9697</v>
       </c>
       <c r="M4" t="n">
-        <v>1.583</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>1.0514</v>
+        <v>0.0132</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5316</v>
+        <v>0.9237</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.5842000000000001</v>
+        <v>-1.5579</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9737</v>
+        <v>-2.3368</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3895</v>
+        <v>0.7789</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3336</v>
+        <v>0.6173999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.371</v>
+        <v>0.2926</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0374</v>
+        <v>0.3249</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. BOTAS FERNANDEZ</t>
+          <t>P. TRUÑO SOMS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9372</v>
+        <v>1.2237</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3416</v>
+        <v>1.2237</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5956</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>2.8555</v>
+        <v>1.2237</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0379</v>
+        <v>0.6158</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8935</v>
+        <v>0.6079</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9185</v>
+        <v>1.2237</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.0512</v>
+        <v>0.6158</v>
       </c>
       <c r="L5" t="n">
-        <v>1.9697</v>
+        <v>0.6079</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9370000000000001</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0132</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9237</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.5579</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.3368</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7789</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2505</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1301</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1204</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>0.89</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.89</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. TRUÑO SOMS</t>
+          <t>J. VALEIRAS CREUS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2237</v>
+        <v>0.9097</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2237</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.2873</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2237</v>
+        <v>-1.3763</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6158</v>
+        <v>-1.8268</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6079</v>
+        <v>0.4506</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2237</v>
+        <v>-2.2055</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6158</v>
+        <v>-1.2007</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6079</v>
+        <v>-1.0048</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>0.8292</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-0.6262</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.4554</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.7789</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.3632</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.7865</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.8165</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.2795</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.4421</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-2.7216</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8589</v>
+        <v>0.6803</v>
       </c>
       <c r="E7" t="n">
-        <v>4.0069</v>
+        <v>4.1065</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.148</v>
+        <v>-3.4262</v>
       </c>
       <c r="G7" t="n">
         <v>0.4663</v>
@@ -1000,13 +1000,13 @@
         <v>0.5842000000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.108</v>
+        <v>-0.2866</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4947</v>
+        <v>-0.395</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3867</v>
+        <v>0.1084</v>
       </c>
       <c r="V7" t="n">
         <v>0.89</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. SALAS MERCHAN</t>
+          <t>L. SIGISMONTI RODRIGUEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.304</v>
+        <v>0.6161</v>
       </c>
       <c r="E8" t="n">
-        <v>1.3174</v>
+        <v>-1.2132</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0134</v>
+        <v>1.8293</v>
       </c>
       <c r="G8" t="n">
-        <v>2.4263</v>
+        <v>1.8424</v>
       </c>
       <c r="H8" t="n">
-        <v>0.549</v>
+        <v>-0.4676</v>
       </c>
       <c r="I8" t="n">
-        <v>1.8773</v>
+        <v>2.31</v>
       </c>
       <c r="J8" t="n">
-        <v>2.6617</v>
+        <v>1.2067</v>
       </c>
       <c r="K8" t="n">
-        <v>1.4292</v>
+        <v>-0.1795</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2325</v>
+        <v>1.3863</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2353</v>
+        <v>0.6357</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8802</v>
+        <v>-0.288</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6448</v>
+        <v>0.9237</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3895</v>
+        <v>-1.3632</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.3895</v>
+        <v>-2.3368</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7789</v>
+        <v>0.9737</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8719</v>
+        <v>0.1368</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5722</v>
+        <v>-0.083</v>
       </c>
       <c r="U8" t="n">
-        <v>1.4441</v>
+        <v>0.2199</v>
       </c>
       <c r="V8" t="n">
-        <v>-3.3837</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.3826</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.0011</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. REVELLES DIAZ</t>
+          <t>R. SALAS MERCHAN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3829</v>
+        <v>0.0041</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3939</v>
+        <v>1.3792</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0111</v>
+        <v>-1.3751</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.9163</v>
+        <v>2.4263</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.3603</v>
+        <v>0.549</v>
       </c>
       <c r="I9" t="n">
-        <v>0.444</v>
+        <v>1.8773</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2454</v>
+        <v>2.6617</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.9749</v>
+        <v>1.4292</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7295</v>
+        <v>1.2325</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6709000000000001</v>
+        <v>-0.2353</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3855</v>
+        <v>-0.8802</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2855</v>
+        <v>0.6448</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.3895</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1684</v>
+        <v>-0.3895</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1684</v>
+        <v>0.7789</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4081</v>
+        <v>0.572</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2012</v>
+        <v>-0.5104</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2069</v>
+        <v>1.0823</v>
       </c>
       <c r="V9" t="n">
-        <v>0.9416</v>
+        <v>-3.3837</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2211</v>
+        <v>-0.3826</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2795</v>
+        <v>-3.0011</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. TRUNO SOMS</t>
+          <t>R. REVELLES DIAZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6149</v>
+        <v>-0.2599</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7797</v>
+        <v>-0.4936</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1648</v>
+        <v>0.2337</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.03</v>
+        <v>-0.9163</v>
       </c>
       <c r="H10" t="n">
-        <v>1.249</v>
+        <v>-1.3603</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.279</v>
+        <v>0.444</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4594</v>
+        <v>-0.2454</v>
       </c>
       <c r="K10" t="n">
-        <v>1.5857</v>
+        <v>-0.9749</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.1264</v>
+        <v>0.7295</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4893</v>
+        <v>-0.6709000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3367</v>
+        <v>-0.3855</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1526</v>
+        <v>-0.2855</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9737</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.1947</v>
+        <v>-1.1684</v>
       </c>
       <c r="R10" t="n">
         <v>1.1684</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5655</v>
+        <v>-0.2852</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0512</v>
+        <v>-0.3009</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4857</v>
+        <v>0.0157</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.9932</v>
+        <v>0.9416</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.9932</v>
+        <v>1.2211</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L. SIGISMONTI RODRIGUEZ</t>
+          <t>P. TRUNO SOMS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.6551</v>
+        <v>-0.411</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2339</v>
+        <v>-1.381</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5788</v>
+        <v>0.97</v>
       </c>
       <c r="G11" t="n">
-        <v>1.8424</v>
+        <v>-0.03</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4676</v>
+        <v>1.249</v>
       </c>
       <c r="I11" t="n">
-        <v>2.31</v>
+        <v>-1.279</v>
       </c>
       <c r="J11" t="n">
-        <v>1.2067</v>
+        <v>0.4594</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.1795</v>
+        <v>1.5857</v>
       </c>
       <c r="L11" t="n">
-        <v>1.3863</v>
+        <v>-1.1264</v>
       </c>
       <c r="M11" t="n">
-        <v>0.6357</v>
+        <v>-0.4893</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.288</v>
+        <v>-0.3367</v>
       </c>
       <c r="O11" t="n">
-        <v>0.9237</v>
+        <v>-0.1526</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.3632</v>
+        <v>0.9737</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.3368</v>
+        <v>-0.1947</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9737</v>
+        <v>1.1684</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1344</v>
+        <v>-0.3616</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1038</v>
+        <v>-0.6525</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0306</v>
+        <v>0.2909</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.9932</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.9932</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.3551</v>
+        <v>-1.9062</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.9361</v>
+        <v>-3.3759</v>
       </c>
       <c r="F12" t="n">
-        <v>1.581</v>
+        <v>1.4697</v>
       </c>
       <c r="G12" t="n">
         <v>-1.7766</v>
@@ -1390,13 +1390,13 @@
         <v>0.9737</v>
       </c>
       <c r="S12" t="n">
-        <v>0.031</v>
+        <v>0.4799</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4854</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5165</v>
+        <v>0.4052</v>
       </c>
       <c r="V12" t="n">
         <v>0.5590000000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.3072</v>
+        <v>-3.5963</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.5966</v>
+        <v>-3.1361</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7106</v>
+        <v>-0.4602</v>
       </c>
       <c r="G13" t="n">
         <v>-1.2532</v>
@@ -1468,13 +1468,13 @@
         <v>0.1947</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8593</v>
+        <v>-0.1484</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6183</v>
+        <v>-0.1578</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.241</v>
+        <v>0.0095</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2211</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.9489</v>
+        <v>10.5671</v>
       </c>
       <c r="E14" t="n">
-        <v>5.313499999999999</v>
+        <v>5.931599999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>4.6355</v>
+        <v>4.635599999999998</v>
       </c>
       <c r="G14" t="n">
         <v>10.2895</v>
@@ -1546,13 +1546,13 @@
         <v>9.736800000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>2.519600000000001</v>
+        <v>3.137699999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.2549</v>
+        <v>-0.6366999999999998</v>
       </c>
       <c r="U14" t="n">
-        <v>3.7747</v>
+        <v>3.7746</v>
       </c>
       <c r="V14" t="n">
         <v>2.0078</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I. SALAZAR ORTEGA</t>
+          <t>I. BETOLAZA BELOKI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.67</v>
+        <v>2.8412</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9509</v>
+        <v>1.7754</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.281</v>
+        <v>1.0658</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.6471</v>
+        <v>2.2431</v>
       </c>
       <c r="H15" t="n">
-        <v>1.2368</v>
+        <v>2.6597</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.8839</v>
+        <v>-0.4166</v>
       </c>
       <c r="J15" t="n">
-        <v>1.4093</v>
+        <v>2.8561</v>
       </c>
       <c r="K15" t="n">
-        <v>1.9117</v>
+        <v>1.632</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5024</v>
+        <v>1.2241</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.0564</v>
+        <v>-0.613</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6749000000000001</v>
+        <v>1.0277</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.3815</v>
+        <v>-1.6407</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9737</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q15" t="n">
         <v>-0.9737</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9474</v>
+        <v>1.5579</v>
       </c>
       <c r="S15" t="n">
-        <v>2.0123</v>
+        <v>0.0138</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4043</v>
+        <v>-0.107</v>
       </c>
       <c r="U15" t="n">
-        <v>1.6081</v>
+        <v>0.1209</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3311</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>2.1111</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. BETOLAZA BELOKI</t>
+          <t>M. SAINZ DE LA MAZA GARRASTACHU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2863</v>
+        <v>1.625</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5761</v>
+        <v>1.7096</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7103</v>
+        <v>-0.08459999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>2.2431</v>
+        <v>0.6851</v>
       </c>
       <c r="H16" t="n">
-        <v>2.6597</v>
+        <v>2.8849</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4166</v>
+        <v>-2.1997</v>
       </c>
       <c r="J16" t="n">
-        <v>2.8561</v>
+        <v>2.4888</v>
       </c>
       <c r="K16" t="n">
-        <v>1.632</v>
+        <v>2.4966</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2241</v>
+        <v>-0.0077</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.613</v>
+        <v>-1.8037</v>
       </c>
       <c r="N16" t="n">
-        <v>1.0277</v>
+        <v>0.3883</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.6407</v>
+        <v>-2.192</v>
       </c>
       <c r="P16" t="n">
         <v>0.5842000000000001</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9737</v>
+        <v>-1.9474</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5579</v>
+        <v>2.5316</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.541</v>
+        <v>-0.2033</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3064</v>
+        <v>-0.6119</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2346</v>
+        <v>0.4086</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. SAINZ DE LA MAZA GARRASTACHU</t>
+          <t>I. SALAZAR ORTEGA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2441</v>
+        <v>0.9497</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2112</v>
+        <v>1.9542</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0329</v>
+        <v>-1.0045</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6851</v>
+        <v>-0.6471</v>
       </c>
       <c r="H17" t="n">
-        <v>2.8849</v>
+        <v>1.2368</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.1997</v>
+        <v>-1.8839</v>
       </c>
       <c r="J17" t="n">
-        <v>2.4888</v>
+        <v>1.4093</v>
       </c>
       <c r="K17" t="n">
-        <v>2.4966</v>
+        <v>1.9117</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.0077</v>
+        <v>-0.5024</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.8037</v>
+        <v>-2.0564</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3883</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.192</v>
+        <v>-1.3815</v>
       </c>
       <c r="P17" t="n">
-        <v>0.5842000000000001</v>
+        <v>0.9737</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9474</v>
+        <v>-0.9737</v>
       </c>
       <c r="R17" t="n">
-        <v>2.5316</v>
+        <v>1.9474</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5841</v>
+        <v>0.2921</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1102</v>
+        <v>-0.5925</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5261</v>
+        <v>0.8846000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.3311</v>
       </c>
       <c r="W17" t="n">
-        <v>1.78</v>
+        <v>2.1111</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2211</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1653</v>
+        <v>0.5395</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4882</v>
+        <v>0.8869</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6535</v>
+        <v>-0.3475</v>
       </c>
       <c r="G18" t="n">
         <v>1.6614</v>
@@ -1858,13 +1858,13 @@
         <v>1.1684</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1314</v>
+        <v>-0.4266</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8657</v>
+        <v>-0.467</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2657</v>
+        <v>0.0404</v>
       </c>
       <c r="V18" t="n">
         <v>-0.89</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. NDIAYE SOW</t>
+          <t>J. PEREZ BENITO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4125</v>
+        <v>-0.4131</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0624</v>
+        <v>-0.5765</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.4749</v>
+        <v>0.1634</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5493</v>
+        <v>-2.6766</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0045</v>
+        <v>0.7306</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5447</v>
+        <v>-3.4072</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.9954</v>
+        <v>-1.1636</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.9954</v>
+        <v>0.8621</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-2.0257</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4461</v>
+        <v>-1.513</v>
       </c>
       <c r="N19" t="n">
-        <v>0.9908</v>
+        <v>-0.1315</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5447</v>
+        <v>-1.3815</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9737</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.9474</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9737</v>
+        <v>1.9474</v>
       </c>
       <c r="S19" t="n">
-        <v>1.6567</v>
+        <v>-0.8408</v>
       </c>
       <c r="T19" t="n">
-        <v>1.4988</v>
+        <v>-1.1287</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1579</v>
+        <v>0.2879</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.4937</v>
+        <v>3.1042</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5590000000000001</v>
+        <v>3.6632</v>
       </c>
       <c r="X19" t="n">
-        <v>-3.0526</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. PEREZ BENITO</t>
+          <t>I. PEDROSA BELLES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9231</v>
+        <v>-1.4643</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9752</v>
+        <v>-1.2338</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0521</v>
+        <v>-0.2305</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.6766</v>
+        <v>-0.8726</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7306</v>
+        <v>0.2961</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.4072</v>
+        <v>-1.1687</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.1636</v>
+        <v>-1.1859</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8621</v>
+        <v>-0.5619</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.0257</v>
+        <v>-0.624</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.513</v>
+        <v>0.3132</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1315</v>
+        <v>0.8579</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.3815</v>
+        <v>-0.5447</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9474</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.9474</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.3508</v>
+        <v>-0.2859</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.5274</v>
+        <v>-0.048</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1766</v>
+        <v>-0.2379</v>
       </c>
       <c r="V20" t="n">
-        <v>3.1042</v>
+        <v>-0.89</v>
       </c>
       <c r="W20" t="n">
-        <v>3.6632</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. PEDROSA BELLES</t>
+          <t>M. NDIAYE SOW</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9357</v>
+        <v>-1.5268</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.4332</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5024999999999999</v>
+        <v>-1.5925</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.8726</v>
+        <v>-0.5493</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2961</v>
+        <v>-0.0045</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.1687</v>
+        <v>-0.5447</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.1859</v>
+        <v>-0.9954</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.5619</v>
+        <v>-0.9954</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.624</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3132</v>
+        <v>0.4461</v>
       </c>
       <c r="N21" t="n">
-        <v>0.8579</v>
+        <v>0.9908</v>
       </c>
       <c r="O21" t="n">
         <v>-0.5447</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5842000000000001</v>
+        <v>0.9737</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.5842000000000001</v>
+        <v>0.9737</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7573</v>
+        <v>0.5424</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2473</v>
+        <v>0.5021</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5099</v>
+        <v>0.0404</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.89</v>
+        <v>-2.4937</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.89</v>
+        <v>-3.0526</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.9593</v>
+        <v>-1.8759</v>
       </c>
       <c r="E22" t="n">
         <v>-1.865</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.09429999999999999</v>
+        <v>-0.0109</v>
       </c>
       <c r="G22" t="n">
         <v>-0.7229</v>
@@ -2170,13 +2170,13 @@
         <v>0.1947</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4575</v>
+        <v>-0.374</v>
       </c>
       <c r="T22" t="n">
         <v>-0.2473</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2102</v>
+        <v>-0.1267</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.3536</v>
+        <v>-2.1211</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3935</v>
+        <v>0.4932</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.7472</v>
+        <v>-2.6143</v>
       </c>
       <c r="G23" t="n">
         <v>0.4206</v>
@@ -2248,13 +2248,13 @@
         <v>1.3632</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4421</v>
+        <v>-0.2095</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3249</v>
+        <v>-0.2252</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1172</v>
+        <v>0.0157</v>
       </c>
       <c r="V23" t="n">
         <v>-2.7216</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.075</v>
+        <v>-2.7851</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.074</v>
+        <v>-2.1737</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.001</v>
+        <v>-0.6115</v>
       </c>
       <c r="G24" t="n">
         <v>-4.4991</v>
@@ -2326,13 +2326,13 @@
         <v>1.1684</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.127</v>
+        <v>0.1629</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1209</v>
+        <v>-0.2206</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0061</v>
+        <v>0.3835</v>
       </c>
       <c r="V24" t="n">
         <v>0.3826</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.3246</v>
+        <v>-5.0534</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.9705</v>
+        <v>-5.6714</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6459</v>
+        <v>0.6181</v>
       </c>
       <c r="G25" t="n">
         <v>-5.3324</v>
@@ -2404,13 +2404,13 @@
         <v>1.1684</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7975</v>
+        <v>-0.5263</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9275</v>
+        <v>-0.6284999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>0.13</v>
+        <v>0.1022</v>
       </c>
       <c r="V25" t="n">
         <v>0.6105</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-9.948699999999999</v>
+        <v>-9.284299999999998</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.6356</v>
+        <v>-4.6355</v>
       </c>
       <c r="F26" t="n">
-        <v>-5.313199999999999</v>
+        <v>-4.649</v>
       </c>
       <c r="G26" t="n">
         <v>-10.2898</v>
@@ -2455,7 +2455,7 @@
         <v>-13.487</v>
       </c>
       <c r="J26" t="n">
-        <v>-2.2385</v>
+        <v>-2.238500000000001</v>
       </c>
       <c r="K26" t="n">
         <v>1.6175</v>
@@ -2482,13 +2482,13 @@
         <v>14.6053</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.519699999999999</v>
+        <v>-1.8552</v>
       </c>
       <c r="T26" t="n">
-        <v>-3.7745</v>
+        <v>-3.7746</v>
       </c>
       <c r="U26" t="n">
-        <v>1.255</v>
+        <v>1.9196</v>
       </c>
       <c r="V26" t="n">
         <v>-2.0079</v>
